--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0112.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0112.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>For Ya</t>
+          <t>Vì Ya</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Starfaring</t>
+          <t>Du Hành Giữa Các Vì Sao</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Ngày Ánh Sao Đầu Tiên Đến</t>
+          <t>Ngày Ánh Sao Lướt Tới</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Âm Thanh Chuông Giữa Trưa</t>
+          <t>Âm Thanh Chuông Trưa</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hot Night Inspiration</t>
+          <t>Cảm Hứng Đêm Nóng Bỏng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chân Trời Vũ Trụ</t>
+          <t>Chân Trời Không Gian</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Tương Lai Như Bạn Thấy</t>
+          <t>Tương Lai Như Anh Thấy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Nơi Động Cơ Phản Ứng Tỏa Sáng</t>
+          <t>Nơi Động Cơ Phản Ứng Toả Sáng</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Khi Cây Solistree Ngủ Yên</t>
+          <t>Khi Solistree Thiu Thiu Ngủ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Hãy Nghỉ Ngơi, Bạn Vẫn Ở Nhà</t>
+          <t>Hãy nghỉ ngơi đi, ngươi vẫn còn ở nhà mà.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Những Vì Sao, Mặt Trời và Mọi Thứ Ở Giữa</t>
+          <t>Những Vì Sao, Mặt Trời và Vạn Vật Giữa Chúng</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Celestial Edge</t>
+          <t>Lưỡi Kiếm Của Tinh Tú</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Vùng Đất Những Giấc Mơ Đã Mất</t>
+          <t>Vùng Đất Những Giấc Mơ Chết</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Falling Stars, Wandering Thoughts</t>
+          <t>Những Vì Sao Rơi, Những Suy Tư Lang Thang</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Nhìn Lại Nơi Xa Xôi</t>
+          <t>Nhìn Lại Viễn Xứ</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Giai Điệu Trên Gió</t>
+          <t>Khúc Nhạc Trên Gió</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Từ Vùng Đất Solsvein</t>
+          <t>Từ Solsvein</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Mười Sáu Trăm Triệu Bit</t>
+          <t>Mười Sáu Tỉ Bit</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Aleph-1: Voidmatter Node</t>
+          <t>Aleph-1: Nút Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Warp Zone</t>
+          <t>Khu Vực Dịch Chuyển</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Persona 5 Royal: Collab Track</t>
+          <t>Bài Hát Hợp Tác: Persona 5 Royal</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Persona 5 Royal: Collab Track</t>
+          <t>Bài Hát Hợp Tác: Persona 5 Royal</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Persona 3 Reload: Collab Track</t>
+          <t>Bài Hát Hợp Tác: Persona 3 Reload</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Persona 3 Reload: Collab Track</t>
+          <t>Bài Hát Hợp Tác: Persona 3 Reload</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog: Collab Track</t>
+          <t>Sonic the Hedgehog: Bản Nhạc Hợp Tác</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog: Collab Track</t>
+          <t>Sonic the Hedgehog: Bản Nhạc Hợp Tác</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Dưới Lớp Mặt Nạ</t>
+          <t>Dưới Mặt Nạ</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Life Will Change</t>
+          <t>Sinh Mệnh Sẽ Thay Đổi</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Color Your Night</t>
+          <t>Tô Điểm Đêm Trời</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Full Moon Full Life</t>
+          <t>Trăng Tròn, Sinh Mệnh Đầy Đủ</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Undefeatable</t>
+          <t>Bất Khả Chiến Bại</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Tìm Ngọn lửa của bạn</t>
+          <t>Tìm Your Flame</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Neo-Tide | Remix Album</t>
+          <t>Neo-Tide | Album Remix</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Echoes</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Development Materials</t>
+          <t>Vật liệu Chế tạo</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Resources</t>
+          <t>Tài Nguyên</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Vật Phẩm Nhiệm Vụ</t>
+          <t>Vật phẩm nhiệm vụ</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Valuables</t>
+          <t>Vật Phẩm Quý Giá</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Tiêu hao</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Vật Liệu Kinh Nghiệm Vũ Khí</t>
+          <t>Vật liệu Tăng EXP Vũ Khí</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Vật Liệu Vũ Khí và Kỹ Năng</t>
+          <t>Nguyên Liệu Vũ Khí và Kỹ Năng</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Vật Liệu Nâng Cấp Forte</t>
+          <t>Vật liệu Nâng cấp Tần số</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Special Token</t>
+          <t>Mã Thông Hành Đặc Biệt</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Rương Cung Cấp</t>
+          <t>Supply Chest</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Triệu Tập Token</t>
+          <t>Phiếu Triệu Tập</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Triệu Tập Exchange Token</t>
+          <t>Đổi Phiếu Triệu Tập</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Lunite Subscription Token</t>
+          <t>Phiếu Đăng Ký Lunite</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>EXP</t>
+          <t>Điểm Kinh Nghiệm</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Potion</t>
+          <t>Thuốc Tiềm Năng</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Vật Phẩm Nhiệm Vụ</t>
+          <t>Vật phẩm nhiệm vụ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Vật Liệu Phát Triển Echo</t>
+          <t>Vật Liệu Phát Triển Tiếng Vọng</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Công thức</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Vật Phẩm Đã Chế Tạo</t>
+          <t>Vật phẩm đã xử lý</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Cooking Ingredient</t>
+          <t>Nguyên Liệu Nấu Ăn</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Intimacy</t>
+          <t>Thân Tình</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Influence</t>
+          <t>Ảnh Hưởng</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Remnant Shard</t>
+          <t>Mảnh Dư</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Universal Currency</t>
+          <t>Tiền Tệ Chung</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Podcast Pioneer</t>
+          <t>Podcast Tiên Phong</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Vật Phẩm Nhiệm Vụ</t>
+          <t>Vật phẩm nhiệm vụ</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Crafting Recipe</t>
+          <t>Công thức chế tác</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Synthesis Recipe: Potion Making</t>
+          <t>Công thức Tổng hợp: Chế tạo Thuốc</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Synthesis Result: Potion</t>
+          <t>Kết quả Tổng hợp: Thuốc</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Synthesis Recipe: Constructing</t>
+          <t>Công thức Tổng hợp: Chế tạo Vật phẩm</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Kết Quả Tổng Hợp: Vật Phẩm Trong Game</t>
+          <t>Kết quả Tổng hợp: Vật phẩm Trong Trận</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Premium Currency</t>
+          <t>Tiền Tệ Cao Cấp</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Activity Points</t>
+          <t>Điểm Hoạt Động</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Vật Liệu Vũ Khí và Kỹ Năng</t>
+          <t>Nguyên Liệu Vũ Khí và Kỹ Năng</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Ore</t>
+          <t>Quặng</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Vật Liệu Thăng Hoa Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Vật liệu nâng cấp kỹ năng</t>
+          <t>Vật Liệu Nâng Cấp Kỹ Năng</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Vật Liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Taoyuan Vale</t>
+          <t>Thung Lũng Đào Nguyên</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Bell-Borne Ravine</t>
+          <t>Khe Núi Bell-Borne</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Heron Wetland</t>
+          <t>Đầm Lầy Heron</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Tiger's Maw Mine</t>
+          <t>Mỏ Hầm Hổ</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Giant Banyan</t>
+          <t>Cây Đa Khổng Lồ</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Forbidden Forest</t>
+          <t>Rừng Cấm Địa</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Withered Line</t>
+          <t>Dòng Suy Tàn</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Camp Overwatch</t>
+          <t>Giám Sát Trại</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Proximity of Tacet Field</t>
+          <t>Vùng Lân Cận Tổ Tacet</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Vật Liệu Dược Phẩm</t>
+          <t>Nguyên Liệu Dược Phẩm</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Vật Liệu Thăng Hoa</t>
+          <t>Vật liệu thăng hoa</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Vật Liệu Chế Tạo</t>
+          <t>Vật liệu Chế tạo</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Vật Phẩm Sự Kiện</t>
+          <t>Vật phẩm sự kiện</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Melody Box</t>
+          <t>Hộp Giai Điệu</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Token</t>
+          <t>Mã Đổi</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Danh Hiệu</t>
+          <t>Danh hiệu</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Vật Liệu Tái Xây Dựng</t>
+          <t>Vật liệu tái thiết</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Proximity of Coast</t>
+          <t>Vùng Lân Cận Bờ Biển</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Weapon Mold</t>
+          <t>Tiêu Chuẩn Vũ khí Mold</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Wear</t>
+          <t>Mặc</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Đang mặc Chim Bồ Câu Tự Do Qua Ngày Đêm</t>
+          <t>Mặc bộ Unfettered Dove xuyên ngày đêm</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Đã tháo bỏ Chim Bồ Câu Tự Do Qua Ngày Đêm</t>
+          <t>Đã loại bỏ Unfettered Dove qua Day and Night</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>"Những Vì Sao Sáng Dành Cho Người" đã được trang bị</t>
+          <t>"Ánh Sao Dành Cho Người" đã được trang bị</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>"Những Vì Sao Sáng Dành Cho Người" đã được tháo bỏ</t>
+          <t>"Ánh Sao Dành Cho Người" đã bị gỡ bỏ</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>New Year Theater Photo</t>
+          <t>Ảnh Sân Khấu Tết Mới</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>New Year Theater Photo</t>
+          <t>Ảnh Sân Khấu Tết Mới</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Memory Fragment 2</t>
+          <t>Mảnh Ký Ức 2</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Memory Fragment 1</t>
+          <t>Mảnh Ký Ức 1</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Memory Fragment 5</t>
+          <t>Mảnh Ký Ức 5</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Memory Fragment 3</t>
+          <t>Mảnh Ký Ức 3</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Memory Fragment 4</t>
+          <t>Mảnh Ký Ức 4</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
